--- a/data/trans_orig/P57B3_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57B3_R-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>85937</t>
+          <t>93564</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71293</t>
+          <t>77178</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103287</t>
+          <t>113629</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>101963</t>
+          <t>111677</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87866</t>
+          <t>97128</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117466</t>
+          <t>126484</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>187899</t>
+          <t>205241</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>166856</t>
+          <t>183810</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>210109</t>
+          <t>233015</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>549504</t>
+          <t>597146</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>532154</t>
+          <t>577081</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>564148</t>
+          <t>613532</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>572148</t>
+          <t>619702</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>556645</t>
+          <t>604895</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>586245</t>
+          <t>634251</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1121654</t>
+          <t>1216847</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1099444</t>
+          <t>1189073</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1142697</t>
+          <t>1238278</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,07%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674111</t>
+          <t>731379</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674111</t>
+          <t>731379</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674111</t>
+          <t>731379</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1309553</t>
+          <t>1422088</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1309553</t>
+          <t>1422088</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1309553</t>
+          <t>1422088</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>356620</t>
+          <t>132796</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>130198</t>
+          <t>112450</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>798581</t>
+          <t>153786</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>147631</t>
+          <t>171225</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130958</t>
+          <t>150621</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>169754</t>
+          <t>193211</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>504252</t>
+          <t>304021</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>280092</t>
+          <t>273643</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1060418</t>
+          <t>333396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>835219</t>
+          <t>914967</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393258</t>
+          <t>893977</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1061641</t>
+          <t>935313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>809425</t>
+          <t>898465</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>787302</t>
+          <t>876479</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>826098</t>
+          <t>919069</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1644643</t>
+          <t>1813432</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1088477</t>
+          <t>1784057</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1868803</t>
+          <t>1843810</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1191839</t>
+          <t>1047763</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1191839</t>
+          <t>1047763</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1191839</t>
+          <t>1047763</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957056</t>
+          <t>1069690</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957056</t>
+          <t>1069690</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957056</t>
+          <t>1069690</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2148895</t>
+          <t>2117453</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2148895</t>
+          <t>2117453</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2148895</t>
+          <t>2117453</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>64399</t>
+          <t>71994</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51014</t>
+          <t>58002</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82941</t>
+          <t>90125</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>64584</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30702</t>
+          <t>60798</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88747</t>
+          <t>91580</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>128983</t>
+          <t>146994</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84658</t>
+          <t>123894</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159947</t>
+          <t>171490</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>639414</t>
+          <t>730151</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620872</t>
+          <t>712020</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>652799</t>
+          <t>744143</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>867690</t>
+          <t>736075</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>843527</t>
+          <t>719495</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>901572</t>
+          <t>750277</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1507104</t>
+          <t>1466227</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1476140</t>
+          <t>1441731</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1551429</t>
+          <t>1489327</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703813</t>
+          <t>802145</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703813</t>
+          <t>802145</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703813</t>
+          <t>802145</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932274</t>
+          <t>811075</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932274</t>
+          <t>811075</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932274</t>
+          <t>811075</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1636087</t>
+          <t>1613221</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1636087</t>
+          <t>1613221</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1636087</t>
+          <t>1613221</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>102378</t>
+          <t>118686</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85864</t>
+          <t>99717</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120401</t>
+          <t>137866</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>126312</t>
+          <t>146904</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98798</t>
+          <t>128735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146411</t>
+          <t>166602</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>228690</t>
+          <t>265590</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>198649</t>
+          <t>238584</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>255992</t>
+          <t>293083</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
+          <t>12,61%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>11,32%</t>
         </is>
       </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>824453</t>
+          <t>871376</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>806430</t>
+          <t>852196</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>840967</t>
+          <t>890345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>966579</t>
+          <t>970012</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>946480</t>
+          <t>950314</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>994093</t>
+          <t>988181</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1791033</t>
+          <t>1841388</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1763731</t>
+          <t>1813895</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1821074</t>
+          <t>1868394</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
+          <t>87,39%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>86,09%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>88,68%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>87,33%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>90,16%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1092891</t>
+          <t>1116916</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1092891</t>
+          <t>1116916</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1092891</t>
+          <t>1116916</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2019723</t>
+          <t>2106978</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2019723</t>
+          <t>2106978</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2019723</t>
+          <t>2106978</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>609334</t>
+          <t>417039</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>379463</t>
+          <t>378278</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1280857</t>
+          <t>460031</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>440490</t>
+          <t>504807</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>358236</t>
+          <t>470570</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>482937</t>
+          <t>542857</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1049824</t>
+          <t>921846</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>820712</t>
+          <t>872490</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1872786</t>
+          <t>975451</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2848590</t>
+          <t>3113641</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2177067</t>
+          <t>3070649</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3078461</t>
+          <t>3152402</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3215843</t>
+          <t>3224253</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3173396</t>
+          <t>3186203</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3298097</t>
+          <t>3258490</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6064433</t>
+          <t>6337894</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5241471</t>
+          <t>6284289</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6293545</t>
+          <t>6387250</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
